--- a/output/pdf_financials_xlsx/HOM.U.xlsx
+++ b/output/pdf_financials_xlsx/HOM.U.xlsx
@@ -2665,16 +2665,16 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="101">
@@ -8552,7 +8552,11 @@
           <t>Depreciation of right-of-use asset 16</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -9642,7 +9646,11 @@
           <t>Depreciation of right-of-use asset 17</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E180" s="5" t="n">
         <v>0.13</v>
       </c>
